--- a/监考安排导入模板.xlsx
+++ b/监考安排导入模板.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <t>年级</t>
   </si>
@@ -25,6 +25,12 @@
     <t>场次</t>
   </si>
   <si>
+    <t>开始时间</t>
+  </si>
+  <si>
+    <t>结束时间</t>
+  </si>
+  <si>
     <t>学科</t>
   </si>
   <si>
@@ -52,13 +58,31 @@
     <t>2026-05-11</t>
   </si>
   <si>
-    <t>第一场(08:00-10:00)</t>
-  </si>
-  <si>
-    <t>第二场(10:20-12:00)</t>
-  </si>
-  <si>
-    <t>第三场(14:00-16:00)</t>
+    <t>第一场</t>
+  </si>
+  <si>
+    <t>第二场</t>
+  </si>
+  <si>
+    <t>第三场</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
   </si>
   <si>
     <t>语文</t>
@@ -482,10 +506,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,143 +531,185 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
         <v>31</v>
       </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F7" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>36</v>
+      <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/监考安排导入模板.xlsx
+++ b/监考安排导入模板.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>年级</t>
   </si>
@@ -22,9 +22,6 @@
     <t>日期</t>
   </si>
   <si>
-    <t>场次</t>
-  </si>
-  <si>
     <t>开始时间</t>
   </si>
   <si>
@@ -56,15 +53,6 @@
   </si>
   <si>
     <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>第一场</t>
-  </si>
-  <si>
-    <t>第二场</t>
-  </si>
-  <si>
-    <t>第三场</t>
   </si>
   <si>
     <t>08:00</t>
@@ -506,10 +494,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,182 +522,161 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
